--- a/artfynd/A 58856-2025 artfynd.xlsx
+++ b/artfynd/A 58856-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112912787</v>
+        <v>112912727</v>
       </c>
       <c r="B2" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405237</v>
+        <v>405119</v>
       </c>
       <c r="R2" t="n">
-        <v>6716630</v>
+        <v>6716499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>112912744</v>
       </c>
       <c r="B3" t="n">
-        <v>74199</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404936</v>
+        <v>404935</v>
       </c>
       <c r="R3" t="n">
-        <v>6716346</v>
+        <v>6716347</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112912735</v>
+        <v>112912724</v>
       </c>
       <c r="B4" t="n">
-        <v>78113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405049</v>
+        <v>405157</v>
       </c>
       <c r="R4" t="n">
-        <v>6716451</v>
+        <v>6716433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112912725</v>
+        <v>112912729</v>
       </c>
       <c r="B5" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405127</v>
+        <v>405107</v>
       </c>
       <c r="R5" t="n">
-        <v>6716455</v>
+        <v>6716478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112912730</v>
+        <v>112912736</v>
       </c>
       <c r="B6" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405116</v>
+        <v>405053</v>
       </c>
       <c r="R6" t="n">
-        <v>6716465</v>
+        <v>6716494</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112912727</v>
+        <v>112912738</v>
       </c>
       <c r="B7" t="n">
-        <v>74199</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405118</v>
+        <v>405016</v>
       </c>
       <c r="R7" t="n">
-        <v>6716499</v>
+        <v>6716448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112912742</v>
+        <v>112912786</v>
       </c>
       <c r="B8" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404960</v>
+        <v>405163</v>
       </c>
       <c r="R8" t="n">
-        <v>6716315</v>
+        <v>6716448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112912780</v>
+        <v>112912784</v>
       </c>
       <c r="B9" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404951</v>
+        <v>405159</v>
       </c>
       <c r="R9" t="n">
-        <v>6716352</v>
+        <v>6716441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112912737</v>
+        <v>112912788</v>
       </c>
       <c r="B10" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404987</v>
+        <v>405249</v>
       </c>
       <c r="R10" t="n">
-        <v>6716416</v>
+        <v>6716639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112912729</v>
+        <v>112912725</v>
       </c>
       <c r="B11" t="n">
-        <v>77696</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405107</v>
+        <v>405127</v>
       </c>
       <c r="R11" t="n">
-        <v>6716478</v>
+        <v>6716455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112912736</v>
+        <v>112912726</v>
       </c>
       <c r="B12" t="n">
-        <v>77696</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405053</v>
+        <v>405112</v>
       </c>
       <c r="R12" t="n">
-        <v>6716494</v>
+        <v>6716511</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112912759</v>
+        <v>112912728</v>
       </c>
       <c r="B13" t="n">
-        <v>79046</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404956</v>
+        <v>405051</v>
       </c>
       <c r="R13" t="n">
-        <v>6716326</v>
+        <v>6716498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112912738</v>
+        <v>112912730</v>
       </c>
       <c r="B14" t="n">
-        <v>77696</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405016</v>
+        <v>405116</v>
       </c>
       <c r="R14" t="n">
-        <v>6716449</v>
+        <v>6716465</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112912728</v>
+        <v>112912731</v>
       </c>
       <c r="B15" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405050</v>
+        <v>405126</v>
       </c>
       <c r="R15" t="n">
-        <v>6716498</v>
+        <v>6716458</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112912760</v>
+        <v>112912733</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404956</v>
+        <v>405098</v>
       </c>
       <c r="R16" t="n">
-        <v>6716326</v>
+        <v>6716465</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112912762</v>
+        <v>112912737</v>
       </c>
       <c r="B17" t="n">
-        <v>78617</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405013</v>
+        <v>404986</v>
       </c>
       <c r="R17" t="n">
-        <v>6716446</v>
+        <v>6716416</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,19 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112912726</v>
+        <v>112912742</v>
       </c>
       <c r="B18" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405111</v>
+        <v>404960</v>
       </c>
       <c r="R18" t="n">
-        <v>6716510</v>
+        <v>6716315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112912732</v>
+        <v>112912780</v>
       </c>
       <c r="B19" t="n">
-        <v>78113</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405079</v>
+        <v>404950</v>
       </c>
       <c r="R19" t="n">
-        <v>6716515</v>
+        <v>6716352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,19 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112912733</v>
+        <v>112912782</v>
       </c>
       <c r="B20" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405098</v>
+        <v>405161</v>
       </c>
       <c r="R20" t="n">
-        <v>6716466</v>
+        <v>6716448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112912734</v>
+        <v>112912785</v>
       </c>
       <c r="B21" t="n">
-        <v>78617</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405055</v>
+        <v>405176</v>
       </c>
       <c r="R21" t="n">
-        <v>6716505</v>
+        <v>6716459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,19 +2615,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112912731</v>
+        <v>112912787</v>
       </c>
       <c r="B22" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405126</v>
+        <v>405237</v>
       </c>
       <c r="R22" t="n">
-        <v>6716458</v>
+        <v>6716630</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,16 +2715,11 @@
         <v>112912723</v>
       </c>
       <c r="B23" t="n">
-        <v>78113</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2860,7 +2750,7 @@
         <v>405103</v>
       </c>
       <c r="R23" t="n">
-        <v>6716518</v>
+        <v>6716517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,6 +2806,588 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112912732</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>405079</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6716515</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112912735</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>405049</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6716451</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112912734</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>405054</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6716505</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112912762</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>405013</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6716445</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112912760</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>404956</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6716326</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112912759</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>404956</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6716326</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58856-2025 artfynd.xlsx
+++ b/artfynd/A 58856-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912729</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912736</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912738</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912786</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912784</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912788</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912725</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912726</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912728</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912730</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912731</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912737</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912780</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912782</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912785</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912787</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912723</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912732</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912735</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912734</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912762</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912760</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,8 +3528,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112912759</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>